--- a/tramites/Plantillas/Excel/FORMATOVACANCIAUSICAMM.xlsx
+++ b/tramites/Plantillas/Excel/FORMATOVACANCIAUSICAMM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\control_maestros\gestion_escolar\templates\tramites\Plantillas\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\control_maestros\tramites\Plantillas\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>nivel educativo</t>
   </si>
@@ -362,9 +362,6 @@
   </si>
   <si>
     <t>Nombre</t>
-  </si>
-  <si>
-    <t>MLGM/snm</t>
   </si>
   <si>
     <t>DR. JESUS MANUEL LUNA ESPINOZA</t>
@@ -1046,7 +1043,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -1116,7 +1113,7 @@
       </c>
       <c r="AA1" s="4"/>
     </row>
-    <row r="2" spans="1:27" s="11" customFormat="1" ht="18.75">
+    <row r="2" spans="1:27" s="11" customFormat="1" ht="57" customHeight="1">
       <c r="A2" s="20"/>
       <c r="B2" s="21"/>
       <c r="C2" s="20"/>
@@ -1172,7 +1169,7 @@
       <c r="Y3" s="16"/>
       <c r="Z3" s="16"/>
     </row>
-    <row r="4" spans="1:27" s="11" customFormat="1" ht="18.75">
+    <row r="4" spans="1:27" s="11" customFormat="1" ht="73.5" customHeight="1">
       <c r="A4" s="20"/>
       <c r="B4" s="21"/>
       <c r="C4" s="20"/>
@@ -1707,7 +1704,7 @@
       <c r="F38" s="39"/>
       <c r="G38" s="5"/>
       <c r="H38" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O38" s="7"/>
       <c r="Q38" s="42" t="s">
@@ -1748,7 +1745,7 @@
     </row>
     <row r="40" spans="1:21" ht="20.25" customHeight="1">
       <c r="A40" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B40" s="37"/>
       <c r="C40" s="37"/>
@@ -1757,7 +1754,7 @@
       <c r="F40" s="37"/>
       <c r="G40" s="5"/>
       <c r="H40" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I40" s="40"/>
       <c r="J40" s="40"/>
@@ -1767,7 +1764,7 @@
       <c r="N40" s="40"/>
       <c r="O40" s="7"/>
       <c r="Q40" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="37"/>
@@ -1776,7 +1773,7 @@
     </row>
     <row r="41" spans="1:21" ht="20.25" customHeight="1">
       <c r="A41" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B41" s="36"/>
       <c r="C41" s="36"/>
@@ -1785,7 +1782,7 @@
       <c r="F41" s="36"/>
       <c r="G41" s="5"/>
       <c r="H41" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I41" s="41"/>
       <c r="J41" s="41"/>
@@ -1795,7 +1792,7 @@
       <c r="N41" s="41"/>
       <c r="O41" s="7"/>
       <c r="Q41" s="36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R41" s="36"/>
       <c r="S41" s="36"/>
@@ -1878,9 +1875,6 @@
       <c r="U46" s="5"/>
     </row>
     <row r="47" spans="1:21">
-      <c r="A47" t="s">
-        <v>95</v>
-      </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -16727,7 +16721,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="26.25">
       <c r="A1" s="35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15" customHeight="1">
@@ -16767,7 +16761,7 @@
     </row>
     <row r="9" spans="1:1" ht="15" customHeight="1">
       <c r="A9" s="31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" customHeight="1">
@@ -16777,7 +16771,7 @@
     </row>
     <row r="11" spans="1:1" ht="15" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15" customHeight="1">
@@ -16887,7 +16881,7 @@
     </row>
     <row r="33" spans="1:1" ht="15" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
@@ -16912,7 +16906,7 @@
     </row>
     <row r="38" spans="1:1" ht="15" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15" customHeight="1">
@@ -16922,7 +16916,7 @@
     </row>
     <row r="40" spans="1:1" ht="15" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="15" customHeight="1">
@@ -16937,7 +16931,7 @@
     </row>
     <row r="43" spans="1:1" ht="15" customHeight="1">
       <c r="A43" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15" customHeight="1">
@@ -17007,72 +17001,72 @@
     </row>
     <row r="57" spans="1:1" ht="15" customHeight="1">
       <c r="A57" s="33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="15" customHeight="1">
       <c r="A58" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="15" customHeight="1">
       <c r="A59" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="15" customHeight="1">
       <c r="A60" s="33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="15" customHeight="1">
       <c r="A61" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="15" customHeight="1">
       <c r="A62" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="15" customHeight="1">
       <c r="A63" s="32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="15" customHeight="1">
       <c r="A64" s="31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="15" customHeight="1">
       <c r="A65" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="15" customHeight="1">
       <c r="A66" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="15" customHeight="1">
       <c r="A67" s="33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="15" customHeight="1">
       <c r="A68" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="15" customHeight="1">
       <c r="A69" s="32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="15" customHeight="1">
       <c r="A70" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="15" customHeight="1">
@@ -17869,7 +17863,7 @@
     </row>
     <row r="8" spans="1:1" ht="15" customHeight="1">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1"/>
